--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEB6B9E-44F3-4512-ADC6-3EE4BC7F1A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F36A5D-3FE7-405E-9D67-3A4E7D91C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>Бондаренко Пётр Алексеевич</t>
   </si>
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>Колисова Екатерина Викторовна</t>
+  </si>
+  <si>
+    <t>Филиппов Всеволод Александрович</t>
+  </si>
+  <si>
+    <t>Б04-307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filippov.va@phystech.edu </t>
   </si>
 </sst>
 </file>
@@ -584,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96196530-19EE-440F-B004-34F8391F510C}">
-  <dimension ref="C4:F26"/>
+  <dimension ref="C4:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
@@ -623,7 +632,7 @@
     </row>
     <row r="6" spans="3:6" ht="15.75">
       <c r="C6" s="1">
-        <f t="shared" ref="C6:C26" si="0">C5+1</f>
+        <f t="shared" ref="C6:C27" si="0">C5+1</f>
         <v>3</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -882,13 +891,13 @@
         <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="3:6" ht="15.75">
@@ -897,10 +906,10 @@
         <v>21</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>2</v>
@@ -912,10 +921,10 @@
         <v>22</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>2</v>
@@ -927,12 +936,27 @@
         <v>23</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" ht="15.75">
+      <c r="C27" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>2</v>
       </c>
     </row>
@@ -955,10 +979,10 @@
     <hyperlink ref="E20" r:id="rId15" display="mailto:sumerkin.vd@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="E21" r:id="rId16" display="mailto:tarasov.aiu@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="E22" r:id="rId17" display="mailto:titov.ea@phystech.edu" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E23" r:id="rId18" display="mailto:khusainov.bi@phystech.edu" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E24" r:id="rId19" display="mailto:sharipov.ka@phystech.edu" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="E25" r:id="rId20" display="mailto:shinkarenko.ve@phystech.edu" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E26" r:id="rId21" display="mailto:esedullaev.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E24" r:id="rId18" display="mailto:khusainov.bi@phystech.edu" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="E25" r:id="rId19" display="mailto:sharipov.ka@phystech.edu" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E26" r:id="rId20" display="mailto:shinkarenko.ve@phystech.edu" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="E27" r:id="rId21" display="mailto:esedullaev.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
     <hyperlink ref="E7" r:id="rId22" display="mailto:grigorev.aleksandr@phystech.edu" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F36A5D-3FE7-405E-9D67-3A4E7D91C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D5345F-C4EE-4E8E-9DA0-2EA60576536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="посещаемость" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
   <si>
     <t>Бондаренко Пётр Алексеевич</t>
   </si>
@@ -193,6 +194,9 @@
   </si>
   <si>
     <t xml:space="preserve">filippov.va@phystech.edu </t>
+  </si>
+  <si>
+    <t>по</t>
   </si>
 </sst>
 </file>
@@ -261,7 +265,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -278,6 +282,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -987,4 +993,700 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579EB211-EF6F-4556-82BE-912AE19589F8}">
+  <dimension ref="A1:T30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="9">
+        <v>45689</v>
+      </c>
+      <c r="I7" s="9">
+        <v>45696</v>
+      </c>
+      <c r="J7" s="9">
+        <v>45710</v>
+      </c>
+      <c r="K7" s="9">
+        <v>45717</v>
+      </c>
+      <c r="L7" s="9">
+        <v>45731</v>
+      </c>
+      <c r="M7" s="9">
+        <v>45738</v>
+      </c>
+      <c r="N7" s="9">
+        <v>45745</v>
+      </c>
+      <c r="O7" s="9">
+        <v>45752</v>
+      </c>
+      <c r="P7" s="9">
+        <v>45759</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>45766</v>
+      </c>
+      <c r="R7" s="9">
+        <v>45773</v>
+      </c>
+      <c r="S7" s="9">
+        <v>45780</v>
+      </c>
+      <c r="T7" s="9">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="E9" s="8">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="E10" s="8">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="E11" s="8">
+        <v>4</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="E12" s="8">
+        <v>5</v>
+      </c>
+      <c r="F12" s="8">
+        <v>3</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="E13" s="8">
+        <v>6</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="E14" s="8">
+        <v>7</v>
+      </c>
+      <c r="F14" s="8">
+        <v>4</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="E15" s="8">
+        <v>8</v>
+      </c>
+      <c r="F15" s="8">
+        <v>3</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="E16" s="8">
+        <v>9</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+    </row>
+    <row r="17" spans="5:20">
+      <c r="E17" s="8">
+        <v>10</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+    </row>
+    <row r="18" spans="5:20">
+      <c r="E18" s="8">
+        <v>11</v>
+      </c>
+      <c r="F18" s="8">
+        <v>4</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+    </row>
+    <row r="19" spans="5:20">
+      <c r="E19" s="8">
+        <v>12</v>
+      </c>
+      <c r="F19" s="8">
+        <v>3</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+    </row>
+    <row r="20" spans="5:20">
+      <c r="E20" s="8">
+        <v>13</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+    </row>
+    <row r="21" spans="5:20">
+      <c r="E21" s="8">
+        <v>14</v>
+      </c>
+      <c r="F21" s="8">
+        <v>4</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+    </row>
+    <row r="22" spans="5:20">
+      <c r="E22" s="8">
+        <v>15</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+    </row>
+    <row r="23" spans="5:20">
+      <c r="E23" s="8">
+        <v>16</v>
+      </c>
+      <c r="F23" s="8">
+        <v>3</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1</v>
+      </c>
+      <c r="K23" s="8">
+        <v>1</v>
+      </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+    </row>
+    <row r="24" spans="5:20">
+      <c r="E24" s="8">
+        <v>17</v>
+      </c>
+      <c r="F24" s="8">
+        <v>3</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8">
+        <v>1</v>
+      </c>
+      <c r="K24" s="8">
+        <v>1</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+    </row>
+    <row r="25" spans="5:20">
+      <c r="E25" s="8">
+        <v>18</v>
+      </c>
+      <c r="F25" s="8">
+        <v>3</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8">
+        <v>1</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8">
+        <v>1</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+    </row>
+    <row r="26" spans="5:20">
+      <c r="E26" s="8">
+        <v>19</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+    </row>
+    <row r="27" spans="5:20">
+      <c r="E27" s="8">
+        <v>20</v>
+      </c>
+      <c r="F27" s="8">
+        <v>1</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="8">
+        <v>1</v>
+      </c>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+    </row>
+    <row r="28" spans="5:20">
+      <c r="E28" s="8">
+        <v>21</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+    </row>
+    <row r="29" spans="5:20">
+      <c r="E29" s="8">
+        <v>22</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+      <c r="K29" s="8">
+        <v>1</v>
+      </c>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+    </row>
+    <row r="30" spans="5:20">
+      <c r="E30" s="8">
+        <v>23</v>
+      </c>
+      <c r="F30" s="8">
+        <v>1</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D5345F-C4EE-4E8E-9DA0-2EA60576536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B20A22-83C1-483E-99A0-1DC38B3C9BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
   <si>
     <t>Бондаренко Пётр Алексеевич</t>
   </si>
@@ -88,12 +88,6 @@
     <t>idrisov.sergei@phystech.edu</t>
   </si>
   <si>
-    <t>Ильясов Тагир Ильгизович</t>
-  </si>
-  <si>
-    <t>ilyasov.tagir@phystech.edu</t>
-  </si>
-  <si>
     <t>Кротюк Александр Алексеевич</t>
   </si>
   <si>
@@ -145,22 +139,10 @@
     <t>tarasov.aiu@phystech.edu</t>
   </si>
   <si>
-    <t>Титов Евгений Алексеевич</t>
-  </si>
-  <si>
-    <t>titov.ea@phystech.edu</t>
-  </si>
-  <si>
     <t>Хусаинов Билал Ильгизович</t>
   </si>
   <si>
     <t>khusainov.bi@phystech.edu</t>
-  </si>
-  <si>
-    <t>Шарипов Кирилл Алексеевич</t>
-  </si>
-  <si>
-    <t>sharipov.ka@phystech.edu</t>
   </si>
   <si>
     <t>Шинкаренко Владислав Эдуардович</t>
@@ -599,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96196530-19EE-440F-B004-34F8391F510C}">
-  <dimension ref="C4:F27"/>
+  <dimension ref="C4:F24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
@@ -638,7 +620,7 @@
     </row>
     <row r="6" spans="3:6" ht="15.75">
       <c r="C6" s="1">
-        <f t="shared" ref="C6:C27" si="0">C5+1</f>
+        <f t="shared" ref="C6:C24" si="0">C5+1</f>
         <v>3</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -657,10 +639,10 @@
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>2</v>
@@ -731,11 +713,11 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>17</v>
+      <c r="D12" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>2</v>
@@ -746,11 +728,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>49</v>
+      <c r="D13" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>2</v>
@@ -776,14 +758,14 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>2</v>
+      <c r="F15" s="6" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="3:6" ht="15.75">
@@ -791,14 +773,14 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>5</v>
+      <c r="F16" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="15.75">
@@ -821,14 +803,14 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>27</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>2</v>
+      <c r="F18" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="3:6" ht="15.75">
@@ -836,14 +818,14 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>29</v>
+      <c r="D19" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="6" t="s">
         <v>31</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="3:6" ht="15.75">
@@ -867,13 +849,13 @@
         <v>18</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="3:6" ht="15.75">
@@ -882,10 +864,10 @@
         <v>19</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>2</v>
@@ -897,13 +879,13 @@
         <v>20</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="3:6" ht="15.75">
@@ -918,51 +900,6 @@
         <v>39</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6" ht="15.75">
-      <c r="C25" s="1">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6" ht="15.75">
-      <c r="C26" s="1">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6" ht="15.75">
-      <c r="C27" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="5" t="s">
         <v>2</v>
       </c>
     </row>
@@ -974,22 +911,19 @@
     <hyperlink ref="E8" r:id="rId4" display="mailto:dubenkov.vm@phystech.edu" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="E9" r:id="rId5" display="mailto:evtushenko.os@phystech.edu" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="E10" r:id="rId6" display="mailto:zelenin.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E11" r:id="rId7" display="mailto:idrisov.sergei@phystech.edu" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E12" r:id="rId8" display="mailto:ilyasov.tagir@phystech.edu" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E14" r:id="rId9" display="mailto:krotiuk.aa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E15" r:id="rId10" display="mailto:penskaia.dp@phystech.edu" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E16" r:id="rId11" display="mailto:piskunova.av@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E17" r:id="rId12" display="mailto:piterskaia.es@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E18" r:id="rId13" display="mailto:reshetov.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E19" r:id="rId14" display="mailto:suvorov.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E20" r:id="rId15" display="mailto:sumerkin.vd@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E21" r:id="rId16" display="mailto:tarasov.aiu@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E22" r:id="rId17" display="mailto:titov.ea@phystech.edu" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E24" r:id="rId18" display="mailto:khusainov.bi@phystech.edu" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E25" r:id="rId19" display="mailto:sharipov.ka@phystech.edu" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="E26" r:id="rId20" display="mailto:shinkarenko.ve@phystech.edu" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E27" r:id="rId21" display="mailto:esedullaev.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="E7" r:id="rId22" display="mailto:grigorev.aleksandr@phystech.edu" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="E13" r:id="rId7" display="mailto:krotiuk.aa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E14" r:id="rId8" display="mailto:penskaia.dp@phystech.edu" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E15" r:id="rId9" display="mailto:piskunova.av@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E16" r:id="rId10" display="mailto:piterskaia.es@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E17" r:id="rId11" display="mailto:reshetov.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E18" r:id="rId12" display="mailto:suvorov.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="E19" r:id="rId13" display="mailto:sumerkin.vd@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E20" r:id="rId14" display="mailto:tarasov.aiu@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E22" r:id="rId15" display="mailto:khusainov.bi@phystech.edu" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="E23" r:id="rId16" display="mailto:shinkarenko.ve@phystech.edu" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="E24" r:id="rId17" display="mailto:esedullaev.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E7" r:id="rId18" display="mailto:grigorev.aleksandr@phystech.edu" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="E11" r:id="rId19" display="mailto:idrisov.sergei@phystech.edu" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -997,7 +931,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579EB211-EF6F-4556-82BE-912AE19589F8}">
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="7" max="7" width="41.5703125" customWidth="1"/>
@@ -1005,7 +939,7 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1078,6 +1012,7 @@
     </row>
     <row r="9" spans="1:20">
       <c r="E9" s="8">
+        <f>1+E8</f>
         <v>2</v>
       </c>
       <c r="F9" s="8">
@@ -1106,6 +1041,7 @@
     </row>
     <row r="10" spans="1:20">
       <c r="E10" s="8">
+        <f t="shared" ref="E10:E28" si="0">1+E9</f>
         <v>3</v>
       </c>
       <c r="F10" s="8">
@@ -1130,13 +1066,14 @@
     </row>
     <row r="11" spans="1:20">
       <c r="E11" s="8">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F11" s="8">
         <v>1</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H11" s="8">
         <v>1</v>
@@ -1156,6 +1093,7 @@
     </row>
     <row r="12" spans="1:20">
       <c r="E12" s="8">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="F12" s="8">
@@ -1186,6 +1124,7 @@
     </row>
     <row r="13" spans="1:20">
       <c r="E13" s="8">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="F13" s="8">
@@ -1212,6 +1151,7 @@
     </row>
     <row r="14" spans="1:20">
       <c r="E14" s="8">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="F14" s="8">
@@ -1244,6 +1184,7 @@
     </row>
     <row r="15" spans="1:20">
       <c r="E15" s="8">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F15" s="8">
@@ -1274,15 +1215,18 @@
     </row>
     <row r="16" spans="1:20">
       <c r="E16" s="8">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F16" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
@@ -1298,20 +1242,27 @@
     </row>
     <row r="17" spans="5:20">
       <c r="E17" s="8">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F17" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H17" s="8">
         <v>1</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="I17" s="8">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>1</v>
+      </c>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
@@ -1324,17 +1275,16 @@
     </row>
     <row r="18" spans="5:20">
       <c r="E18" s="8">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="F18" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="8">
-        <v>1</v>
-      </c>
+      <c r="H18" s="8"/>
       <c r="I18" s="8">
         <v>1</v>
       </c>
@@ -1356,24 +1306,19 @@
     </row>
     <row r="19" spans="5:20">
       <c r="E19" s="8">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F19" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="8"/>
-      <c r="I19" s="8">
-        <v>1</v>
-      </c>
-      <c r="J19" s="8">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8">
-        <v>1</v>
-      </c>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
@@ -1386,18 +1331,27 @@
     </row>
     <row r="20" spans="5:20">
       <c r="E20" s="8">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="F20" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1</v>
+      </c>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
@@ -1410,26 +1364,23 @@
     </row>
     <row r="21" spans="5:20">
       <c r="E21" s="8">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="F21" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="8">
-        <v>1</v>
-      </c>
+      <c r="H21" s="8"/>
       <c r="I21" s="8">
         <v>1</v>
       </c>
       <c r="J21" s="8">
         <v>1</v>
       </c>
-      <c r="K21" s="8">
-        <v>1</v>
-      </c>
+      <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -1442,10 +1393,11 @@
     </row>
     <row r="22" spans="5:20">
       <c r="E22" s="8">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="F22" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>27</v>
@@ -1457,7 +1409,9 @@
       <c r="J22" s="8">
         <v>1</v>
       </c>
-      <c r="K22" s="8"/>
+      <c r="K22" s="8">
+        <v>1</v>
+      </c>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -1470,13 +1424,14 @@
     </row>
     <row r="23" spans="5:20">
       <c r="E23" s="8">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="F23" s="8">
         <v>3</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="8">
@@ -1500,6 +1455,7 @@
     </row>
     <row r="24" spans="5:20">
       <c r="E24" s="8">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="F24" s="8">
@@ -1530,24 +1486,22 @@
     </row>
     <row r="25" spans="5:20">
       <c r="E25" s="8">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="F25" s="8">
-        <v>3</v>
+      <c r="F25">
+        <f>SUM(H25:T25)</f>
+        <v>1</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8">
-        <v>1</v>
-      </c>
-      <c r="J25" s="8">
-        <v>1</v>
-      </c>
-      <c r="K25" s="8">
-        <v>1</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="H25" s="8">
+        <v>1</v>
+      </c>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
@@ -1560,15 +1514,18 @@
     </row>
     <row r="26" spans="5:20">
       <c r="E26" s="8">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="F26" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -1584,20 +1541,23 @@
     </row>
     <row r="27" spans="5:20">
       <c r="E27" s="8">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="F27" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H27" s="8">
-        <v>1</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H27" s="8"/>
       <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
+      <c r="J27" s="8">
+        <v>1</v>
+      </c>
+      <c r="K27" s="8">
+        <v>1</v>
+      </c>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
@@ -1610,16 +1570,19 @@
     </row>
     <row r="28" spans="5:20">
       <c r="E28" s="8">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="F28" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
+      <c r="I28" s="8">
+        <v>1</v>
+      </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
@@ -1632,60 +1595,6 @@
       <c r="S28" s="8"/>
       <c r="T28" s="8"/>
     </row>
-    <row r="29" spans="5:20">
-      <c r="E29" s="8">
-        <v>22</v>
-      </c>
-      <c r="F29" s="8">
-        <v>2</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8">
-        <v>1</v>
-      </c>
-      <c r="K29" s="8">
-        <v>1</v>
-      </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-    </row>
-    <row r="30" spans="5:20">
-      <c r="E30" s="8">
-        <v>23</v>
-      </c>
-      <c r="F30" s="8">
-        <v>1</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8">
-        <v>1</v>
-      </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B20A22-83C1-483E-99A0-1DC38B3C9BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE59774-7F8E-47D9-AED9-7D5BDB0C2203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="посещаемость" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="58">
   <si>
     <t>Бондаренко Пётр Алексеевич</t>
   </si>
@@ -179,6 +180,36 @@
   </si>
   <si>
     <t>по</t>
+  </si>
+  <si>
+    <t>итог</t>
+  </si>
+  <si>
+    <t>оценка</t>
+  </si>
+  <si>
+    <t>контест1</t>
+  </si>
+  <si>
+    <t>контест2</t>
+  </si>
+  <si>
+    <t>контест3</t>
+  </si>
+  <si>
+    <t>преза1</t>
+  </si>
+  <si>
+    <t>преза2</t>
+  </si>
+  <si>
+    <t>преза3</t>
+  </si>
+  <si>
+    <t>проект</t>
+  </si>
+  <si>
+    <t>доп</t>
   </si>
 </sst>
 </file>
@@ -1598,4 +1629,601 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114873D3-54E6-4CE2-9201-24ADB3883536}">
+  <dimension ref="D5:O26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="44.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:15">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="4:15">
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8">
+        <f>SUM(F6:M6)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <f>IF(3+N6 &gt; 10, 10, 3 + N6)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="4:15">
+      <c r="D7" s="8">
+        <f>1+D6</f>
+        <v>2</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8">
+        <v>2</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8">
+        <f t="shared" ref="N7:N26" si="0">SUM(F7:M7)</f>
+        <v>2</v>
+      </c>
+      <c r="O7" s="8">
+        <f t="shared" ref="O7:O26" si="1">3+N7</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="4:15">
+      <c r="D8" s="8">
+        <f t="shared" ref="D8:D26" si="2">1+D7</f>
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="4:15">
+      <c r="D9" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="4:15">
+      <c r="D10" s="8">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="4:15">
+      <c r="D11" s="8">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="4:15">
+      <c r="D12" s="8">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8">
+        <v>3</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O12" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="4:15">
+      <c r="D13" s="8">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="4:15">
+      <c r="D14" s="8">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="4:15">
+      <c r="D15" s="8">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="4:15">
+      <c r="D16" s="8">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="4:15">
+      <c r="D17" s="8">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="4:15">
+      <c r="D18" s="8">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8">
+        <v>3</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="4:15">
+      <c r="D19" s="8">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8">
+        <v>3</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O19" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="4:15">
+      <c r="D20" s="8">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8">
+        <v>1</v>
+      </c>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="8">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="4:15">
+      <c r="D21" s="8">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8">
+        <v>3</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="4:15">
+      <c r="D22" s="8">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8">
+        <v>3</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O22" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="4:15">
+      <c r="D23" s="8">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="4:15">
+      <c r="D24" s="8">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="4:15">
+      <c r="D25" s="8">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="4:15">
+      <c r="D26" s="8">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="8">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="O6:O26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE59774-7F8E-47D9-AED9-7D5BDB0C2203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37115965-6F2B-4F60-A0EF-CE8B1963B293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -278,7 +278,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -297,6 +297,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1637,6 +1638,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="44.5703125" customWidth="1"/>
+    <col min="6" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="4:15">
@@ -1680,20 +1684,20 @@
       <c r="E6" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8">
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10">
         <f>SUM(F6:M6)</f>
         <v>0</v>
       </c>
       <c r="O6" s="8">
-        <f>IF(3+N6 &gt; 10, 10, 3 + N6)</f>
+        <f>IF(3+N6 &gt; 10, 10, ROUND(3 + N6,0))</f>
         <v>3</v>
       </c>
     </row>
@@ -1705,22 +1709,22 @@
       <c r="E7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10">
         <v>2</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8">
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10">
         <f t="shared" ref="N7:N26" si="0">SUM(F7:M7)</f>
         <v>2</v>
       </c>
       <c r="O7" s="8">
-        <f t="shared" ref="O7:O26" si="1">3+N7</f>
+        <f t="shared" ref="O7:O26" si="1">IF(3+N7 &gt; 10, 10, ROUND(3 + N7,0))</f>
         <v>5</v>
       </c>
     </row>
@@ -1732,15 +1736,15 @@
       <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8">
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1757,15 +1761,15 @@
       <c r="E9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8">
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1782,15 +1786,15 @@
       <c r="E10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8">
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1807,15 +1811,15 @@
       <c r="E11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8">
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1832,17 +1836,17 @@
       <c r="E12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8">
-        <v>3</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8">
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10">
+        <v>3</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1859,21 +1863,25 @@
       <c r="E13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="F13" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="4:15">
@@ -1884,15 +1892,15 @@
       <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8">
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1909,15 +1917,15 @@
       <c r="E15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8">
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1934,15 +1942,15 @@
       <c r="E16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8">
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1959,21 +1967,27 @@
       <c r="E17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="F17" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="4:15">
@@ -1984,23 +1998,25 @@
       <c r="E18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8">
-        <v>3</v>
-      </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10">
+        <v>3</v>
+      </c>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="4:15">
@@ -2011,17 +2027,17 @@
       <c r="E19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8">
-        <v>3</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8">
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10">
+        <v>3</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2038,17 +2054,17 @@
       <c r="E20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8">
-        <v>1</v>
-      </c>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8">
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2065,17 +2081,17 @@
       <c r="E21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8">
-        <v>3</v>
-      </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8">
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10">
+        <v>3</v>
+      </c>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2092,17 +2108,17 @@
       <c r="E22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8">
-        <v>3</v>
-      </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8">
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10">
+        <v>3</v>
+      </c>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2119,15 +2135,15 @@
       <c r="E23" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8">
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2144,15 +2160,15 @@
       <c r="E24" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8">
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2169,15 +2185,15 @@
       <c r="E25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8">
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2194,15 +2210,15 @@
       <c r="E26" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8">
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2225,5 +2241,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37115965-6F2B-4F60-A0EF-CE8B1963B293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2622D367-00F1-4E1F-9677-9DAC4012D630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1023,6 +1023,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="8">
+        <f>SUM(H8:T8)</f>
         <v>0</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -1048,6 +1049,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="8">
+        <f t="shared" ref="F9:F28" si="0">SUM(H9:T9)</f>
         <v>2</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -1073,10 +1075,11 @@
     </row>
     <row r="10" spans="1:20">
       <c r="E10" s="8">
-        <f t="shared" ref="E10:E28" si="0">1+E9</f>
+        <f t="shared" ref="E10:E28" si="1">1+E9</f>
         <v>3</v>
       </c>
       <c r="F10" s="8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -1098,11 +1101,12 @@
     </row>
     <row r="11" spans="1:20">
       <c r="E11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="F11" s="8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>40</v>
@@ -1114,7 +1118,9 @@
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="M11" s="8">
+        <v>1</v>
+      </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -1125,11 +1131,12 @@
     </row>
     <row r="12" spans="1:20">
       <c r="E12" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="F12" s="8">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>8</v>
@@ -1145,7 +1152,9 @@
         <v>1</v>
       </c>
       <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
+      <c r="M12" s="8">
+        <v>1</v>
+      </c>
       <c r="N12" s="8"/>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -1156,10 +1165,11 @@
     </row>
     <row r="13" spans="1:20">
       <c r="E13" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="F13" s="8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -1183,11 +1193,12 @@
     </row>
     <row r="14" spans="1:20">
       <c r="E14" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="F14" s="8">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>12</v>
@@ -1204,8 +1215,12 @@
       <c r="K14" s="8">
         <v>1</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
+      <c r="L14" s="8">
+        <v>1</v>
+      </c>
+      <c r="M14" s="8">
+        <v>1</v>
+      </c>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -1216,11 +1231,12 @@
     </row>
     <row r="15" spans="1:20">
       <c r="E15" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="F15" s="8">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>15</v>
@@ -1235,9 +1251,15 @@
       <c r="K15" s="8">
         <v>1</v>
       </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
+      <c r="L15" s="8">
+        <v>1</v>
+      </c>
+      <c r="M15" s="8">
+        <v>1</v>
+      </c>
+      <c r="N15" s="8">
+        <v>1</v>
+      </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -1247,11 +1269,12 @@
     </row>
     <row r="16" spans="1:20">
       <c r="E16" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="F16" s="8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>43</v>
@@ -1263,7 +1286,9 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
+      <c r="M16" s="8">
+        <v>1</v>
+      </c>
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -1274,11 +1299,12 @@
     </row>
     <row r="17" spans="5:20">
       <c r="E17" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="F17" s="8">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>17</v>
@@ -1297,7 +1323,9 @@
       </c>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
+      <c r="N17" s="8">
+        <v>1</v>
+      </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
@@ -1307,11 +1335,12 @@
     </row>
     <row r="18" spans="5:20">
       <c r="E18" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="F18" s="8">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>19</v>
@@ -1327,7 +1356,9 @@
         <v>1</v>
       </c>
       <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
+      <c r="M18" s="8">
+        <v>1</v>
+      </c>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -1338,10 +1369,11 @@
     </row>
     <row r="19" spans="5:20">
       <c r="E19" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="F19" s="8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -1363,11 +1395,12 @@
     </row>
     <row r="20" spans="5:20">
       <c r="E20" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="F20" s="8">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>23</v>
@@ -1384,9 +1417,15 @@
       <c r="K20" s="8">
         <v>1</v>
       </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
+      <c r="L20" s="8">
+        <v>1</v>
+      </c>
+      <c r="M20" s="8">
+        <v>1</v>
+      </c>
+      <c r="N20" s="8">
+        <v>1</v>
+      </c>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -1396,11 +1435,12 @@
     </row>
     <row r="21" spans="5:20">
       <c r="E21" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="F21" s="8">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>25</v>
@@ -1413,9 +1453,15 @@
         <v>1</v>
       </c>
       <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+      <c r="M21" s="8">
+        <v>1</v>
+      </c>
+      <c r="N21" s="8">
+        <v>1</v>
+      </c>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -1425,11 +1471,12 @@
     </row>
     <row r="22" spans="5:20">
       <c r="E22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="F22" s="8">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>27</v>
@@ -1444,9 +1491,15 @@
       <c r="K22" s="8">
         <v>1</v>
       </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
+      <c r="L22" s="8">
+        <v>1</v>
+      </c>
+      <c r="M22" s="8">
+        <v>1</v>
+      </c>
+      <c r="N22" s="8">
+        <v>1</v>
+      </c>
       <c r="O22" s="8"/>
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
@@ -1456,11 +1509,12 @@
     </row>
     <row r="23" spans="5:20">
       <c r="E23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="F23" s="8">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>30</v>
@@ -1475,9 +1529,15 @@
       <c r="K23" s="8">
         <v>1</v>
       </c>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8">
+        <v>1</v>
+      </c>
+      <c r="N23" s="8">
+        <v>1</v>
+      </c>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -1487,11 +1547,12 @@
     </row>
     <row r="24" spans="5:20">
       <c r="E24" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="F24" s="8">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>32</v>
@@ -1506,9 +1567,15 @@
       <c r="K24" s="8">
         <v>1</v>
       </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
+      <c r="L24" s="8">
+        <v>1</v>
+      </c>
+      <c r="M24" s="8">
+        <v>1</v>
+      </c>
+      <c r="N24" s="8">
+        <v>1</v>
+      </c>
       <c r="O24" s="8"/>
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
@@ -1518,11 +1585,11 @@
     </row>
     <row r="25" spans="5:20">
       <c r="E25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F25">
-        <f>SUM(H25:T25)</f>
+      <c r="F25" s="8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G25" s="8" t="s">
@@ -1546,11 +1613,12 @@
     </row>
     <row r="26" spans="5:20">
       <c r="E26" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="F26" s="8">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>34</v>
@@ -1562,7 +1630,9 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
+      <c r="M26" s="8">
+        <v>1</v>
+      </c>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
@@ -1573,11 +1643,12 @@
     </row>
     <row r="27" spans="5:20">
       <c r="E27" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="F27" s="8">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>36</v>
@@ -1590,7 +1661,9 @@
       <c r="K27" s="8">
         <v>1</v>
       </c>
-      <c r="L27" s="8"/>
+      <c r="L27" s="8">
+        <v>1</v>
+      </c>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
@@ -1602,10 +1675,11 @@
     </row>
     <row r="28" spans="5:20">
       <c r="E28" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="F28" s="8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G28" s="8" t="s">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2622D367-00F1-4E1F-9677-9DAC4012D630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5337C16-6A28-4D4E-A399-EE1C49BCD102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1943,7 +1943,9 @@
       <c r="G13" s="10">
         <v>1.5</v>
       </c>
-      <c r="H13" s="10"/>
+      <c r="H13" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -1951,11 +1953,11 @@
       <c r="M13" s="10"/>
       <c r="N13" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O13" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="4:15">
@@ -2016,7 +2018,9 @@
       <c r="E16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="10">
+        <v>1.5</v>
+      </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
@@ -2026,11 +2030,11 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="4:15">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5337C16-6A28-4D4E-A399-EE1C49BCD102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56B79C2-847C-400A-B041-4A0541B8DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -209,7 +209,7 @@
     <t>проект</t>
   </si>
   <si>
-    <t>доп</t>
+    <t>доп/опрос</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1713,8 @@
   <cols>
     <col min="5" max="5" width="44.5703125" customWidth="1"/>
     <col min="6" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1916,17 +1917,19 @@
       <c r="I12" s="10">
         <v>3</v>
       </c>
-      <c r="J12" s="10"/>
+      <c r="J12" s="10">
+        <v>2</v>
+      </c>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="4:15">
@@ -2084,17 +2087,19 @@
       <c r="I18" s="10">
         <v>3</v>
       </c>
-      <c r="J18" s="10"/>
+      <c r="J18" s="10">
+        <v>2</v>
+      </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="4:15">
@@ -2105,7 +2110,9 @@
       <c r="E19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="10">
+        <v>1.5</v>
+      </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10">
@@ -2117,11 +2124,11 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="4:15">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56B79C2-847C-400A-B041-4A0541B8DECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6CCC8F-DD89-48D9-A5CC-5F5366D0684A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -1811,9 +1811,15 @@
       <c r="E8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="F8" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -1821,11 +1827,11 @@
       <c r="M8" s="10"/>
       <c r="N8" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -1911,8 +1917,12 @@
       <c r="E12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="F12" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1.5</v>
+      </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10">
         <v>3</v>
@@ -1925,11 +1935,11 @@
       <c r="M12" s="10"/>
       <c r="N12" s="10">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="4:15">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6CCC8F-DD89-48D9-A5CC-5F5366D0684A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7485690-F917-4C42-A14E-B4F5C2B3EFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -1867,8 +1867,12 @@
       <c r="E10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
+      <c r="F10" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1.5</v>
+      </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -1877,11 +1881,11 @@
       <c r="M10" s="10"/>
       <c r="N10" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="4:15">
@@ -1981,21 +1985,27 @@
       <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
+      <c r="F14" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H14" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F14:M14)-3</f>
+        <v>1.5</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="4:15">
@@ -2006,9 +2016,15 @@
       <c r="E15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="F15" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
@@ -2016,11 +2032,11 @@
       <c r="M15" s="10"/>
       <c r="N15" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="4:15">
@@ -2149,8 +2165,12 @@
       <c r="E20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="F20" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="10">
+        <v>1.5</v>
+      </c>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -2161,11 +2181,11 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="4:15">
@@ -2176,8 +2196,12 @@
       <c r="E21" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="F21" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="10">
+        <v>1.5</v>
+      </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10">
         <v>3</v>
@@ -2188,11 +2212,11 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="4:15">
@@ -2255,8 +2279,12 @@
       <c r="E24" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+      <c r="F24" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0.5</v>
+      </c>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
@@ -2265,11 +2293,11 @@
       <c r="M24" s="10"/>
       <c r="N24" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="4:15">
@@ -2280,21 +2308,27 @@
       <c r="E25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="F25" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(F25:M25)-2</f>
+        <v>2.5</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="4:15">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7485690-F917-4C42-A14E-B4F5C2B3EFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08576663-6A1D-4DB2-815C-2B3BCB2F2E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -2348,12 +2348,11 @@
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08576663-6A1D-4DB2-815C-2B3BCB2F2E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8E50C-37BC-4409-829D-7B86725FF8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -1795,7 +1795,7 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
-        <f t="shared" ref="N7:N26" si="0">SUM(F7:M7)</f>
+        <f t="shared" ref="N7:N24" si="0">SUM(F7:M7)</f>
         <v>2</v>
       </c>
       <c r="O7" s="8">
@@ -1903,14 +1903,16 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="M11" s="10">
+        <v>8</v>
+      </c>
       <c r="N11" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O11" s="8">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="4:15">
@@ -2289,15 +2291,17 @@
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
+      <c r="L24" s="10">
+        <v>5</v>
+      </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="4:15">
@@ -2342,12 +2346,15 @@
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
+      <c r="I26" s="10">
+        <v>3</v>
+      </c>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
+        <f>SUM(F26:M26)</f>
         <v>3</v>
       </c>
       <c r="O26" s="8">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8E50C-37BC-4409-829D-7B86725FF8D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B7C4CA-07BC-449C-BC79-8C599A8BC37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
   </bookViews>
@@ -1795,7 +1795,7 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
-        <f t="shared" ref="N7:N24" si="0">SUM(F7:M7)</f>
+        <f t="shared" ref="N7:N25" si="0">SUM(F7:M7)</f>
         <v>2</v>
       </c>
       <c r="O7" s="8">
@@ -2313,10 +2313,10 @@
         <v>36</v>
       </c>
       <c r="F25" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G25" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="10">
         <v>1.5</v>
@@ -2327,7 +2327,7 @@
       <c r="L25" s="10"/>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <f>SUM(F25:M25)-2</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="O25" s="8">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -1,25 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B7C4CA-07BC-449C-BC79-8C599A8BC37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{5095FE22-01A3-44F6-AA25-4FC916027D55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29016" windowHeight="16416" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="посещаемость" sheetId="2" r:id="rId2"/>
     <sheet name="Лист2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -215,7 +209,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -359,7 +353,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -411,7 +405,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -605,23 +599,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96196530-19EE-440F-B004-34F8391F510C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="C4:F24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:6" ht="15.75">
+    <row r="4" spans="3:6" ht="15.6">
       <c r="C4">
         <v>1</v>
       </c>
@@ -635,7 +629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="3:6" ht="15.75">
+    <row r="5" spans="3:6" ht="15.6">
       <c r="C5">
         <f>C4+1</f>
         <v>2</v>
@@ -650,7 +644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:6" ht="15.75">
+    <row r="6" spans="3:6" ht="15.6">
       <c r="C6" s="1">
         <f t="shared" ref="C6:C24" si="0">C5+1</f>
         <v>3</v>
@@ -665,7 +659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:6" ht="15.75">
+    <row r="7" spans="3:6" ht="15.6">
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -680,7 +674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="3:6" ht="15.75">
+    <row r="8" spans="3:6" ht="15.6">
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -695,7 +689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="3:6" ht="15.75">
+    <row r="9" spans="3:6" ht="15.6">
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -710,7 +704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="3:6" ht="15.75">
+    <row r="10" spans="3:6" ht="15.6">
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -725,7 +719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="3:6" ht="15.75">
+    <row r="11" spans="3:6" ht="15.6">
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -740,7 +734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:6" ht="15.75">
+    <row r="12" spans="3:6" ht="15.6">
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -755,7 +749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="3:6" ht="15.75">
+    <row r="13" spans="3:6" ht="15.6">
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -770,7 +764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:6" ht="15.75">
+    <row r="14" spans="3:6" ht="15.6">
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -785,7 +779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="3:6" ht="15.75">
+    <row r="15" spans="3:6" ht="15.6">
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -800,7 +794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="3:6" ht="15.75">
+    <row r="16" spans="3:6" ht="15.6">
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -815,7 +809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="15.75">
+    <row r="17" spans="3:6" ht="15.6">
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -830,7 +824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="15.75">
+    <row r="18" spans="3:6" ht="15.6">
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -845,7 +839,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="15.75">
+    <row r="19" spans="3:6" ht="15.6">
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -860,7 +854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="3:6" ht="15.75">
+    <row r="20" spans="3:6" ht="15.6">
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -875,7 +869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="3:6" ht="15.75">
+    <row r="21" spans="3:6" ht="15.6">
       <c r="C21" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -890,7 +884,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="3:6" ht="15.75">
+    <row r="22" spans="3:6" ht="15.6">
       <c r="C22" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -905,7 +899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="15.75">
+    <row r="23" spans="3:6" ht="15.6">
       <c r="C23" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -920,7 +914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="3:6" ht="15.75">
+    <row r="24" spans="3:6" ht="15.6">
       <c r="C24" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -937,36 +931,36 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" display="mailto:bondarenko.pa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E5" r:id="rId2" display="mailto:balushkin.pa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E6" r:id="rId3" display="mailto:vlasov.aleksei@phystech.edu" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E8" r:id="rId4" display="mailto:dubenkov.vm@phystech.edu" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E9" r:id="rId5" display="mailto:evtushenko.os@phystech.edu" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E10" r:id="rId6" display="mailto:zelenin.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E13" r:id="rId7" display="mailto:krotiuk.aa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E14" r:id="rId8" display="mailto:penskaia.dp@phystech.edu" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E15" r:id="rId9" display="mailto:piskunova.av@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E16" r:id="rId10" display="mailto:piterskaia.es@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E17" r:id="rId11" display="mailto:reshetov.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E18" r:id="rId12" display="mailto:suvorov.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E19" r:id="rId13" display="mailto:sumerkin.vd@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E20" r:id="rId14" display="mailto:tarasov.aiu@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E22" r:id="rId15" display="mailto:khusainov.bi@phystech.edu" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E23" r:id="rId16" display="mailto:shinkarenko.ve@phystech.edu" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E24" r:id="rId17" display="mailto:esedullaev.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="E7" r:id="rId18" display="mailto:grigorev.aleksandr@phystech.edu" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="E11" r:id="rId19" display="mailto:idrisov.sergei@phystech.edu" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E4" r:id="rId1" display="mailto:bondarenko.pa@phystech.edu"/>
+    <hyperlink ref="E5" r:id="rId2" display="mailto:balushkin.pa@phystech.edu"/>
+    <hyperlink ref="E6" r:id="rId3" display="mailto:vlasov.aleksei@phystech.edu"/>
+    <hyperlink ref="E8" r:id="rId4" display="mailto:dubenkov.vm@phystech.edu"/>
+    <hyperlink ref="E9" r:id="rId5" display="mailto:evtushenko.os@phystech.edu"/>
+    <hyperlink ref="E10" r:id="rId6" display="mailto:zelenin.da@phystech.edu"/>
+    <hyperlink ref="E13" r:id="rId7" display="mailto:krotiuk.aa@phystech.edu"/>
+    <hyperlink ref="E14" r:id="rId8" display="mailto:penskaia.dp@phystech.edu"/>
+    <hyperlink ref="E15" r:id="rId9" display="mailto:piskunova.av@phystech.edu"/>
+    <hyperlink ref="E16" r:id="rId10" display="mailto:piterskaia.es@phystech.edu"/>
+    <hyperlink ref="E17" r:id="rId11" display="mailto:reshetov.da@phystech.edu"/>
+    <hyperlink ref="E18" r:id="rId12" display="mailto:suvorov.sa@phystech.edu"/>
+    <hyperlink ref="E19" r:id="rId13" display="mailto:sumerkin.vd@phystech.edu"/>
+    <hyperlink ref="E20" r:id="rId14" display="mailto:tarasov.aiu@phystech.edu"/>
+    <hyperlink ref="E22" r:id="rId15" display="mailto:khusainov.bi@phystech.edu"/>
+    <hyperlink ref="E23" r:id="rId16" display="mailto:shinkarenko.ve@phystech.edu"/>
+    <hyperlink ref="E24" r:id="rId17" display="mailto:esedullaev.sa@phystech.edu"/>
+    <hyperlink ref="E7" r:id="rId18" display="mailto:grigorev.aleksandr@phystech.edu"/>
+    <hyperlink ref="E11" r:id="rId19" display="mailto:idrisov.sergei@phystech.edu"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579EB211-EF6F-4556-82BE-912AE19589F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="41.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1707,15 +1701,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114873D3-54E6-4CE2-9201-24ADB3883536}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="D5:O26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="5" max="5" width="44.5703125" customWidth="1"/>
-    <col min="6" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.5546875" customWidth="1"/>
+    <col min="6" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="4:15">
@@ -2173,7 +2167,9 @@
       <c r="G20" s="10">
         <v>1.5</v>
       </c>
-      <c r="H20" s="10"/>
+      <c r="H20" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -2183,11 +2179,11 @@
       <c r="M20" s="10"/>
       <c r="N20" s="10">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="4:15">
@@ -2366,9 +2362,9 @@
   <conditionalFormatting sqref="O6:O26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="max" val="0"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -1,19 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308D2509-98E2-40F6-8882-8362966CEC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29016" windowHeight="16416" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="посещаемость" sheetId="2" r:id="rId2"/>
     <sheet name="Лист2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -209,7 +215,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -599,23 +605,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C4:F24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:6" ht="15.6">
+    <row r="4" spans="3:6" ht="15.75">
       <c r="C4">
         <v>1</v>
       </c>
@@ -629,7 +635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="3:6" ht="15.6">
+    <row r="5" spans="3:6" ht="15.75">
       <c r="C5">
         <f>C4+1</f>
         <v>2</v>
@@ -644,7 +650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:6" ht="15.6">
+    <row r="6" spans="3:6" ht="15.75">
       <c r="C6" s="1">
         <f t="shared" ref="C6:C24" si="0">C5+1</f>
         <v>3</v>
@@ -659,7 +665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:6" ht="15.6">
+    <row r="7" spans="3:6" ht="15.75">
       <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -674,7 +680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="3:6" ht="15.6">
+    <row r="8" spans="3:6" ht="15.75">
       <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -689,7 +695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="3:6" ht="15.6">
+    <row r="9" spans="3:6" ht="15.75">
       <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -704,7 +710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="3:6" ht="15.6">
+    <row r="10" spans="3:6" ht="15.75">
       <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -719,7 +725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="3:6" ht="15.6">
+    <row r="11" spans="3:6" ht="15.75">
       <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -734,7 +740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="3:6" ht="15.6">
+    <row r="12" spans="3:6" ht="15.75">
       <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -749,7 +755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="3:6" ht="15.6">
+    <row r="13" spans="3:6" ht="15.75">
       <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -764,7 +770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="3:6" ht="15.6">
+    <row r="14" spans="3:6" ht="15.75">
       <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -779,7 +785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="3:6" ht="15.6">
+    <row r="15" spans="3:6" ht="15.75">
       <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -794,7 +800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="3:6" ht="15.6">
+    <row r="16" spans="3:6" ht="15.75">
       <c r="C16" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -809,7 +815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="15.6">
+    <row r="17" spans="3:6" ht="15.75">
       <c r="C17" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -824,7 +830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="15.6">
+    <row r="18" spans="3:6" ht="15.75">
       <c r="C18" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -839,7 +845,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="15.6">
+    <row r="19" spans="3:6" ht="15.75">
       <c r="C19" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -854,7 +860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="3:6" ht="15.6">
+    <row r="20" spans="3:6" ht="15.75">
       <c r="C20" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -869,7 +875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="3:6" ht="15.6">
+    <row r="21" spans="3:6" ht="15.75">
       <c r="C21" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -884,7 +890,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="3:6" ht="15.6">
+    <row r="22" spans="3:6" ht="15.75">
       <c r="C22" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -899,7 +905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="15.6">
+    <row r="23" spans="3:6" ht="15.75">
       <c r="C23" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -914,7 +920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="3:6" ht="15.6">
+    <row r="24" spans="3:6" ht="15.75">
       <c r="C24" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -931,36 +937,36 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" display="mailto:bondarenko.pa@phystech.edu"/>
-    <hyperlink ref="E5" r:id="rId2" display="mailto:balushkin.pa@phystech.edu"/>
-    <hyperlink ref="E6" r:id="rId3" display="mailto:vlasov.aleksei@phystech.edu"/>
-    <hyperlink ref="E8" r:id="rId4" display="mailto:dubenkov.vm@phystech.edu"/>
-    <hyperlink ref="E9" r:id="rId5" display="mailto:evtushenko.os@phystech.edu"/>
-    <hyperlink ref="E10" r:id="rId6" display="mailto:zelenin.da@phystech.edu"/>
-    <hyperlink ref="E13" r:id="rId7" display="mailto:krotiuk.aa@phystech.edu"/>
-    <hyperlink ref="E14" r:id="rId8" display="mailto:penskaia.dp@phystech.edu"/>
-    <hyperlink ref="E15" r:id="rId9" display="mailto:piskunova.av@phystech.edu"/>
-    <hyperlink ref="E16" r:id="rId10" display="mailto:piterskaia.es@phystech.edu"/>
-    <hyperlink ref="E17" r:id="rId11" display="mailto:reshetov.da@phystech.edu"/>
-    <hyperlink ref="E18" r:id="rId12" display="mailto:suvorov.sa@phystech.edu"/>
-    <hyperlink ref="E19" r:id="rId13" display="mailto:sumerkin.vd@phystech.edu"/>
-    <hyperlink ref="E20" r:id="rId14" display="mailto:tarasov.aiu@phystech.edu"/>
-    <hyperlink ref="E22" r:id="rId15" display="mailto:khusainov.bi@phystech.edu"/>
-    <hyperlink ref="E23" r:id="rId16" display="mailto:shinkarenko.ve@phystech.edu"/>
-    <hyperlink ref="E24" r:id="rId17" display="mailto:esedullaev.sa@phystech.edu"/>
-    <hyperlink ref="E7" r:id="rId18" display="mailto:grigorev.aleksandr@phystech.edu"/>
-    <hyperlink ref="E11" r:id="rId19" display="mailto:idrisov.sergei@phystech.edu"/>
+    <hyperlink ref="E4" r:id="rId1" display="mailto:bondarenko.pa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" display="mailto:balushkin.pa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId3" display="mailto:vlasov.aleksei@phystech.edu" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E8" r:id="rId4" display="mailto:dubenkov.vm@phystech.edu" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E9" r:id="rId5" display="mailto:evtushenko.os@phystech.edu" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E10" r:id="rId6" display="mailto:zelenin.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E13" r:id="rId7" display="mailto:krotiuk.aa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E14" r:id="rId8" display="mailto:penskaia.dp@phystech.edu" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E15" r:id="rId9" display="mailto:piskunova.av@phystech.edu" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E16" r:id="rId10" display="mailto:piterskaia.es@phystech.edu" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E17" r:id="rId11" display="mailto:reshetov.da@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E18" r:id="rId12" display="mailto:suvorov.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E19" r:id="rId13" display="mailto:sumerkin.vd@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E20" r:id="rId14" display="mailto:tarasov.aiu@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="E22" r:id="rId15" display="mailto:khusainov.bi@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E23" r:id="rId16" display="mailto:shinkarenko.ve@phystech.edu" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E24" r:id="rId17" display="mailto:esedullaev.sa@phystech.edu" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E7" r:id="rId18" display="mailto:grigorev.aleksandr@phystech.edu" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="E11" r:id="rId19" display="mailto:idrisov.sergei@phystech.edu" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T28"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="41.5546875" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1701,15 +1707,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="D5:O26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="44.5546875" customWidth="1"/>
-    <col min="6" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.5703125" customWidth="1"/>
+    <col min="6" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="4:15">
@@ -2135,8 +2141,12 @@
       <c r="F19" s="10">
         <v>1.5</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I19" s="10">
         <v>3</v>
       </c>
@@ -2146,11 +2156,11 @@
       <c r="M19" s="10"/>
       <c r="N19" s="10">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="4:15">
@@ -2362,9 +2372,9 @@
   <conditionalFormatting sqref="O6:O26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308D2509-98E2-40F6-8882-8362966CEC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E273F4-BA76-4488-AA71-922692099ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,7 +359,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -411,7 +411,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2052,7 +2052,9 @@
       <c r="F16" s="10">
         <v>1.5</v>
       </c>
-      <c r="G16" s="10"/>
+      <c r="G16" s="10">
+        <v>1.5</v>
+      </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
@@ -2061,11 +2063,11 @@
       <c r="M16" s="10"/>
       <c r="N16" s="10">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="4:15">
@@ -2210,7 +2212,9 @@
       <c r="G21" s="10">
         <v>1.5</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I21" s="10">
         <v>3</v>
       </c>
@@ -2220,11 +2224,11 @@
       <c r="M21" s="10"/>
       <c r="N21" s="10">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="O21" s="8">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="4:15">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E273F4-BA76-4488-AA71-922692099ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5F1570-FAC6-4DA0-B08F-0BB53B0F4D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1873,7 +1873,9 @@
       <c r="G10" s="10">
         <v>1.5</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="10">
+        <v>0.5</v>
+      </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
@@ -1881,11 +1883,11 @@
       <c r="M10" s="10"/>
       <c r="N10" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="4:15">

--- a/studentsList.xlsx
+++ b/studentsList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspace\с++ practice\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5F1570-FAC6-4DA0-B08F-0BB53B0F4D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F07321-CB4A-447F-83BB-5E2C5185FF76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -305,6 +305,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF8696B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2032,15 +2037,17 @@
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+      <c r="L15" s="10">
+        <v>1</v>
+      </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="O15" s="8">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="4:15">
@@ -2241,7 +2248,9 @@
       <c r="E22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="10">
+        <v>1.5</v>
+      </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10">
@@ -2253,11 +2262,11 @@
       <c r="M22" s="10"/>
       <c r="N22" s="10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O22" s="8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="4:15">
@@ -2376,7 +2385,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="O6:O26">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2386,6 +2395,46 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFC000"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFC000"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFC000"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
